--- a/data/clean/DIM_Agents.xlsx
+++ b/data/clean/DIM_Agents.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Agent, One</t>
+          <t>Agent One</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
@@ -488,7 +488,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Agent, Two</t>
+          <t>Agent Two</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
@@ -513,7 +513,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Agent, Eight</t>
+          <t>Agent Eight</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Agent, Three</t>
+          <t>Agent Three</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Agent, Four</t>
+          <t>Agent Four</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Agent, Five</t>
+          <t>Agent Five</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Agent, Six</t>
+          <t>Agent Six</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Agent, Seven</t>
+          <t>Agent Seven</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
